--- a/Turate/Turate_Basket.xlsx
+++ b/Turate/Turate_Basket.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matteovezzoli/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matteovezzoli/Desktop/Turate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4AEBB6-13EA-A342-AF1C-BEF5128EEC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F644F5BE-1631-E148-81AD-224566F89D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19820" xr2:uid="{77520E61-4CBE-564E-BF0B-ECF911E0A7F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
   <si>
     <t>Giocatori</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Nic</t>
+  </si>
+  <si>
+    <t>Albese</t>
+  </si>
+  <si>
+    <t>BlackMamba</t>
   </si>
 </sst>
 </file>
@@ -534,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71195EE-B1BE-684C-B5EE-A346702C9F57}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -646,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F14" si="0">IF(D3=0,0,D3/E3)</f>
+        <f t="shared" ref="F3:F40" si="0">IF(D3=0,0,D3/E3)</f>
         <v>0.5</v>
       </c>
       <c r="G3" s="2">
@@ -1105,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="3"/>
+        <f>D12*2+G12*3+J12</f>
         <v>0</v>
       </c>
     </row>
@@ -1211,6 +1217,1270 @@
       <c r="N14">
         <f>SUM(N2:N13)</f>
         <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" ref="I15:I40" si="4">IF(G15=0,0,G15/H15)</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" ref="L15:L40" si="5">IF(J15=0,0,J15/K15)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <f>D15*2+G15*3+J15</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ref="N16:N25" si="6">D16*2+G16*3+J16</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>7</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="4"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f>D26*2+G26*3+J26</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <f>SUM(C15:C26)</f>
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <f t="shared" ref="D27:N27" si="7">SUM(D15:D26)</f>
+        <v>21</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="7"/>
+        <v>37</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.56756756756756754</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="4"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="L27" s="3">
+        <f t="shared" si="5"/>
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="7"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <f>D28*2+G28*3+J28</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="4"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="M29">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <f t="shared" ref="N29:N39" si="8">D29*2+G29*3+J29</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>5</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>4</v>
+      </c>
+      <c r="L31" s="3">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="M32">
+        <v>5</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39" s="3">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40">
+        <f>SUM(C28:C39)</f>
+        <v>5</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:N40" si="9">SUM(D28:D39)</f>
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="9"/>
+        <v>39</v>
+      </c>
+      <c r="F40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="9"/>
+        <v>27</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="4"/>
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="L40" s="3">
+        <f t="shared" si="5"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="9"/>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1221,7 +2491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633EA45B-43FE-4341-8C19-B983639FAE4C}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -1264,6 +2534,46 @@
         <v>97</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3">
+        <v>75</v>
+      </c>
+      <c r="F3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>46</v>
+      </c>
+      <c r="F4">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Turate/Turate_Basket.xlsx
+++ b/Turate/Turate_Basket.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
   <si>
     <t xml:space="preserve">Partita</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">Palle rubate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giocato</t>
   </si>
   <si>
     <t xml:space="preserve">Jack</t>
@@ -451,7 +454,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultColWidth="10.69140625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -509,13 +512,16 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -563,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
@@ -611,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -659,7 +665,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
@@ -707,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
@@ -755,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -803,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
@@ -851,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0</v>
@@ -899,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
@@ -947,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -995,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -1043,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -1091,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="n">
         <f aca="false">SUM(C2:C13)</f>
@@ -1147,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>1</v>
@@ -1195,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>1</v>
@@ -1243,7 +1249,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>1</v>
@@ -1291,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
@@ -1339,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>1</v>
@@ -1387,7 +1393,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
@@ -1435,7 +1441,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -1483,7 +1489,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0</v>
@@ -1531,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0</v>
@@ -1579,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0</v>
@@ -1627,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0</v>
@@ -1675,7 +1681,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>0</v>
@@ -1723,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1" t="n">
         <f aca="false">SUM(C15:C26)</f>
@@ -1779,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -1827,7 +1833,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
@@ -1875,7 +1881,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
@@ -1923,7 +1929,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
@@ -1971,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>1</v>
@@ -2019,7 +2025,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
@@ -2067,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -2115,7 +2121,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
@@ -2163,7 +2169,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0</v>
@@ -2211,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>0</v>
@@ -2259,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>0</v>
@@ -2307,7 +2313,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>0</v>
@@ -2355,7 +2361,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="1" t="n">
         <f aca="false">SUM(C28:C39)</f>
@@ -2411,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>1</v>
@@ -2471,7 +2477,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>1</v>
@@ -2531,7 +2537,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>1</v>
@@ -2591,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>0</v>
@@ -2651,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>1</v>
@@ -2711,7 +2717,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>0</v>
@@ -2771,7 +2777,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>0</v>
@@ -2831,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>0</v>
@@ -2891,7 +2897,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>0</v>
@@ -2951,7 +2957,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>0</v>
@@ -3011,7 +3017,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>1</v>
@@ -3071,7 +3077,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>0</v>
@@ -3131,7 +3137,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C53" s="1" t="n">
         <f aca="false">SUM(C41:C52)</f>
@@ -3203,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>1</v>
@@ -3257,13 +3263,16 @@
       <c r="R54" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="S54" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>1</v>
@@ -3317,13 +3326,16 @@
       <c r="R55" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="S55" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>1</v>
@@ -3377,13 +3389,16 @@
       <c r="R56" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S56" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>0</v>
@@ -3437,13 +3452,16 @@
       <c r="R57" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="S57" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>1</v>
@@ -3497,13 +3515,16 @@
       <c r="R58" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="S58" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>0</v>
@@ -3557,13 +3578,16 @@
       <c r="R59" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="S59" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>0</v>
@@ -3617,13 +3641,16 @@
       <c r="R60" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S60" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>1</v>
@@ -3676,6 +3703,9 @@
       </c>
       <c r="R61" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="S61" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3683,7 +3713,7 @@
         <v>5</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>0</v>
@@ -3736,6 +3766,9 @@
       </c>
       <c r="R62" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="S62" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3743,7 +3776,7 @@
         <v>5</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>0</v>
@@ -3796,6 +3829,9 @@
       </c>
       <c r="R63" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="S63" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3803,7 +3839,7 @@
         <v>5</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>0</v>
@@ -3855,6 +3891,9 @@
         <v>0</v>
       </c>
       <c r="R64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3863,7 +3902,7 @@
         <v>5</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>0</v>
@@ -3916,6 +3955,9 @@
       </c>
       <c r="R65" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="S65" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3923,7 +3965,7 @@
         <v>5</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C66" s="1" t="n">
         <f aca="false">SUM(C54:C65)</f>
@@ -3988,6 +4030,10 @@
       <c r="R66" s="1" t="n">
         <f aca="false">SUM(R54:R65)</f>
         <v>16</v>
+      </c>
+      <c r="S66" s="0" t="n">
+        <f aca="false">SUM(S54:S65)</f>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4011,22 +4057,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4037,10 +4083,10 @@
         <v>46287</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>81</v>
@@ -4057,10 +4103,10 @@
         <v>46299</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>75</v>
@@ -4077,10 +4123,10 @@
         <v>46299</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>46</v>
@@ -4097,10 +4143,10 @@
         <v>46312</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>72</v>
@@ -4117,10 +4163,10 @@
         <v>46320</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>67</v>
